--- a/plot/agent_readable/source_data/source_data_fig_5_c.xlsx
+++ b/plot/agent_readable/source_data/source_data_fig_5_c.xlsx
@@ -7,9 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="wide_paired_scores" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="boxplot_summary_by_form" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="plot_data" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="source_data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -41,11 +39,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
+        <fgColor rgb="002A251F"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -53,16 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="00D8D2C9"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -434,7 +437,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
@@ -1776,1492 +1779,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>form</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>mean</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>sd</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>median</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>q1</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>q3</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>min</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>max</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>-2.24</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>9.079647570252932</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>-2.000000000000007</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>-6</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>3.999999999999993</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>-17.99999999999999</v>
-      </c>
-      <c r="I2" s="2" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>-0.6399999999999997</v>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>10.6727066232829</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>-6</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>2.000000000000007</v>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>-20</v>
-      </c>
-      <c r="I3" s="2" t="n">
-        <v>24.00000000000001</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F51"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>student_id</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>form</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>training_setting</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Human</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>MAS</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>mas_minus_human</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>S001</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>68</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>66</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>S002</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>54</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>52</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>S003</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>-12</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>S004</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>S005</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>64</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>56.00000000000001</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>-7.999999999999993</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>S006</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>54</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>60</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>S007</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>60</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>52</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>-8</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>S008</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>68</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>62</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>-6</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>S009</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>74</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>56.00000000000001</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>-17.99999999999999</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>S010</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="n">
-        <v>64</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>68</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>S011</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>54</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>48</v>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>-6</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>S012</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="n">
-        <v>70</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>68</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>S013</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>non_main</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>68</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>52</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>-16</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>S014</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>76</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>72</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>-4</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>S015</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>non_main</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="n">
-        <v>54</v>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>57.99999999999999</v>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>3.999999999999993</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>S016</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>non_main</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="n">
-        <v>57.99999999999999</v>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>52</v>
-      </c>
-      <c r="F17" s="2" t="n">
-        <v>-5.999999999999993</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>S017</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>non_main</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="F18" s="2" t="n">
-        <v>-16</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>S018</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>non_main</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="n">
-        <v>57.99999999999999</v>
-      </c>
-      <c r="E19" s="2" t="n">
-        <v>57.99999999999999</v>
-      </c>
-      <c r="F19" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>S019</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>non_main</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="n">
-        <v>60</v>
-      </c>
-      <c r="E20" s="2" t="n">
-        <v>54</v>
-      </c>
-      <c r="F20" s="2" t="n">
-        <v>-6</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>S020</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>non_main</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="n">
-        <v>68</v>
-      </c>
-      <c r="E21" s="2" t="n">
-        <v>64</v>
-      </c>
-      <c r="F21" s="2" t="n">
-        <v>-4</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>S021</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="n">
-        <v>56.00000000000001</v>
-      </c>
-      <c r="E22" s="2" t="n">
-        <v>54</v>
-      </c>
-      <c r="F22" s="2" t="n">
-        <v>-2.000000000000007</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>S022</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="n">
-        <v>44</v>
-      </c>
-      <c r="E23" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="F23" s="2" t="n">
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>S023</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>non_main</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="n">
-        <v>74</v>
-      </c>
-      <c r="E24" s="2" t="n">
-        <v>88</v>
-      </c>
-      <c r="F24" s="2" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>S024</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>non_main</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="n">
-        <v>70</v>
-      </c>
-      <c r="E25" s="2" t="n">
-        <v>88</v>
-      </c>
-      <c r="F25" s="2" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>S025</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>non_main</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="n">
-        <v>70</v>
-      </c>
-      <c r="E26" s="2" t="n">
-        <v>84</v>
-      </c>
-      <c r="F26" s="2" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>S026</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="n">
-        <v>72</v>
-      </c>
-      <c r="E27" s="2" t="n">
-        <v>62</v>
-      </c>
-      <c r="F27" s="2" t="n">
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>S027</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="n">
-        <v>64</v>
-      </c>
-      <c r="E28" s="2" t="n">
-        <v>64</v>
-      </c>
-      <c r="F28" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>S028</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="n">
-        <v>82</v>
-      </c>
-      <c r="E29" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="F29" s="2" t="n">
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>S029</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>non_main</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="E30" s="2" t="n">
-        <v>86</v>
-      </c>
-      <c r="F30" s="2" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>S030</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>non_main</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="n">
-        <v>60</v>
-      </c>
-      <c r="E31" s="2" t="n">
-        <v>68</v>
-      </c>
-      <c r="F31" s="2" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>S031</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>non_main</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="E32" s="2" t="n">
-        <v>56.00000000000001</v>
-      </c>
-      <c r="F32" s="2" t="n">
-        <v>24.00000000000001</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>S032</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>non_main</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="E33" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="F33" s="2" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>S033</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="n">
-        <v>72</v>
-      </c>
-      <c r="E34" s="2" t="n">
-        <v>66</v>
-      </c>
-      <c r="F34" s="2" t="n">
-        <v>-6</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>S034</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="n">
-        <v>82</v>
-      </c>
-      <c r="E35" s="2" t="n">
-        <v>78</v>
-      </c>
-      <c r="F35" s="2" t="n">
-        <v>-4</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>S035</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>non_main</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="n">
-        <v>78</v>
-      </c>
-      <c r="E36" s="2" t="n">
-        <v>82</v>
-      </c>
-      <c r="F36" s="2" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>S036</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>non_main</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="n">
-        <v>76</v>
-      </c>
-      <c r="E37" s="2" t="n">
-        <v>76</v>
-      </c>
-      <c r="F37" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>S037</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>non_main</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="n">
-        <v>78</v>
-      </c>
-      <c r="E38" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="F38" s="2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>S038</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="n">
-        <v>56.00000000000001</v>
-      </c>
-      <c r="E39" s="2" t="n">
-        <v>52</v>
-      </c>
-      <c r="F39" s="2" t="n">
-        <v>-4.000000000000007</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>S039</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>non_main</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="n">
-        <v>48</v>
-      </c>
-      <c r="E40" s="2" t="n">
-        <v>48</v>
-      </c>
-      <c r="F40" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>S040</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="n">
-        <v>57.99999999999999</v>
-      </c>
-      <c r="E41" s="2" t="n">
-        <v>57.99999999999999</v>
-      </c>
-      <c r="F41" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>S041</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="n">
-        <v>66</v>
-      </c>
-      <c r="E42" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="F42" s="2" t="n">
-        <v>-20</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>S042</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="n">
-        <v>57.99999999999999</v>
-      </c>
-      <c r="E43" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F43" s="2" t="n">
-        <v>-7.999999999999993</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>S043</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="E44" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="F44" s="2" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>S044</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="n">
-        <v>64</v>
-      </c>
-      <c r="E45" s="2" t="n">
-        <v>62</v>
-      </c>
-      <c r="F45" s="2" t="n">
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>S045</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="n">
-        <v>56.00000000000001</v>
-      </c>
-      <c r="E46" s="2" t="n">
-        <v>54</v>
-      </c>
-      <c r="F46" s="2" t="n">
-        <v>-2.000000000000007</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>S046</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="n">
-        <v>60</v>
-      </c>
-      <c r="E47" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F47" s="2" t="n">
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>S047</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="n">
-        <v>82</v>
-      </c>
-      <c r="E48" s="2" t="n">
-        <v>66</v>
-      </c>
-      <c r="F48" s="2" t="n">
-        <v>-16</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>S048</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="n">
-        <v>82</v>
-      </c>
-      <c r="E49" s="2" t="n">
-        <v>68</v>
-      </c>
-      <c r="F49" s="2" t="n">
-        <v>-14</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>S049</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="n">
-        <v>54</v>
-      </c>
-      <c r="E50" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F50" s="2" t="n">
-        <v>-4</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>S050</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="n">
-        <v>54</v>
-      </c>
-      <c r="E51" s="2" t="n">
-        <v>56.00000000000001</v>
-      </c>
-      <c r="F51" s="2" t="n">
-        <v>2.000000000000007</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>